--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486751_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486751_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.7916</v>
+        <v>4.9051</v>
       </c>
       <c r="E2" t="n">
-        <v>9.257899999999999</v>
+        <v>7.3963</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.4663</v>
+        <v>-2.4912</v>
       </c>
       <c r="G2" t="n">
         <v>1.7325</v>
@@ -610,13 +610,13 @@
         <v>1.7377</v>
       </c>
       <c r="S2" t="n">
-        <v>3.2102</v>
+        <v>1.3238</v>
       </c>
       <c r="T2" t="n">
-        <v>2.9229</v>
+        <v>1.0613</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2874</v>
+        <v>0.2625</v>
       </c>
       <c r="V2" t="n">
         <v>2.0419</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C. LUIS QUINTERO</t>
+          <t>P. GRIMA LORENZO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.4303</v>
+        <v>3.515</v>
       </c>
       <c r="E3" t="n">
-        <v>4.1201</v>
+        <v>6.002</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.6898</v>
+        <v>-2.487</v>
       </c>
       <c r="G3" t="n">
-        <v>2.6909</v>
+        <v>3.805</v>
       </c>
       <c r="H3" t="n">
-        <v>1.3526</v>
+        <v>0.1314</v>
       </c>
       <c r="I3" t="n">
-        <v>1.3384</v>
+        <v>3.6735</v>
       </c>
       <c r="J3" t="n">
-        <v>5.6788</v>
+        <v>6.2477</v>
       </c>
       <c r="K3" t="n">
-        <v>3.8363</v>
+        <v>2.339</v>
       </c>
       <c r="L3" t="n">
-        <v>1.8426</v>
+        <v>3.9087</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.9879</v>
+        <v>-2.4428</v>
       </c>
       <c r="N3" t="n">
-        <v>-2.4837</v>
+        <v>-2.2076</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.5042</v>
+        <v>-0.2352</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.1585</v>
+        <v>0.7723</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.8962</v>
+        <v>-0.9654</v>
       </c>
       <c r="R3" t="n">
         <v>1.7377</v>
       </c>
       <c r="S3" t="n">
-        <v>1.2414</v>
+        <v>0.1655</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1098</v>
+        <v>-0.1798</v>
       </c>
       <c r="U3" t="n">
-        <v>1.1316</v>
+        <v>0.3452</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6565</v>
+        <v>-1.2277</v>
       </c>
       <c r="W3" t="n">
-        <v>1.2277</v>
+        <v>0.8995</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.5712</v>
+        <v>-2.1271</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. GRIMA LORENZO</t>
+          <t>C. LUIS QUINTERO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5057</v>
+        <v>3.2509</v>
       </c>
       <c r="E4" t="n">
-        <v>4.9678</v>
+        <v>4.4373</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.4621</v>
+        <v>-1.1864</v>
       </c>
       <c r="G4" t="n">
-        <v>3.805</v>
+        <v>2.6909</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1314</v>
+        <v>1.3526</v>
       </c>
       <c r="I4" t="n">
-        <v>3.6735</v>
+        <v>1.3384</v>
       </c>
       <c r="J4" t="n">
-        <v>6.2477</v>
+        <v>5.6788</v>
       </c>
       <c r="K4" t="n">
-        <v>2.339</v>
+        <v>3.8363</v>
       </c>
       <c r="L4" t="n">
-        <v>3.9087</v>
+        <v>1.8426</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.4428</v>
+        <v>-2.9879</v>
       </c>
       <c r="N4" t="n">
-        <v>-2.2076</v>
+        <v>-2.4837</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.2352</v>
+        <v>-0.5042</v>
       </c>
       <c r="P4" t="n">
-        <v>0.7723</v>
+        <v>-1.1585</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9654</v>
+        <v>-2.8962</v>
       </c>
       <c r="R4" t="n">
         <v>1.7377</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.8439</v>
+        <v>1.062</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.214</v>
+        <v>0.427</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3701</v>
+        <v>0.635</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.2277</v>
+        <v>0.6565</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8995</v>
+        <v>1.2277</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.1271</v>
+        <v>-0.5712</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.0199</v>
+        <v>1.3167</v>
       </c>
       <c r="E5" t="n">
-        <v>2.5516</v>
+        <v>1.7243</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.5318000000000001</v>
+        <v>-0.4076</v>
       </c>
       <c r="G5" t="n">
         <v>-0.6971000000000001</v>
@@ -844,13 +844,13 @@
         <v>0.9654</v>
       </c>
       <c r="S5" t="n">
-        <v>1.4893</v>
+        <v>0.786</v>
       </c>
       <c r="T5" t="n">
-        <v>1.627</v>
+        <v>0.7996</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1377</v>
+        <v>-0.0136</v>
       </c>
       <c r="V5" t="n">
         <v>1.2277</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6335</v>
+        <v>0.7121</v>
       </c>
       <c r="E6" t="n">
-        <v>1.3497</v>
+        <v>1.4532</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.7161999999999999</v>
+        <v>-0.741</v>
       </c>
       <c r="G6" t="n">
         <v>0.9356</v>
@@ -922,13 +922,13 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0164</v>
+        <v>0.0622</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0552</v>
+        <v>0.0482</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0387</v>
+        <v>0.0139</v>
       </c>
       <c r="V6" t="n">
         <v>-0.2856</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R. GONZALEZ GRANDE</t>
+          <t>P. RODRIGUEZ FAJARDO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3642</v>
+        <v>0.0828</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.8147</v>
+        <v>0.8481</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4505</v>
+        <v>-0.7653</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.06950000000000001</v>
+        <v>1.6816</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.0416</v>
+        <v>-3.1517</v>
       </c>
       <c r="I7" t="n">
-        <v>0.972</v>
+        <v>4.8333</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8759</v>
+        <v>2.5585</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0621</v>
+        <v>-1.8408</v>
       </c>
       <c r="L7" t="n">
-        <v>0.8138</v>
+        <v>4.3993</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.9454</v>
+        <v>-0.8769</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.1036</v>
+        <v>-1.3109</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1582</v>
+        <v>0.434</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.5446</v>
+        <v>-0.5792</v>
       </c>
       <c r="Q7" t="n">
         <v>-1.9308</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3862</v>
+        <v>1.3515</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0223</v>
+        <v>0.1655</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3311</v>
+        <v>0.2204</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3533</v>
+        <v>-0.0549</v>
       </c>
       <c r="V7" t="n">
-        <v>1.2277</v>
+        <v>-1.1851</v>
       </c>
       <c r="W7" t="n">
-        <v>0.5712</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.6565</v>
+        <v>-1.1851</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.3884</v>
+        <v>-0.0423</v>
       </c>
       <c r="E8" t="n">
-        <v>1.0644</v>
+        <v>1.485</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.4528</v>
+        <v>-1.5273</v>
       </c>
       <c r="G8" t="n">
         <v>-0.0808</v>
@@ -1078,13 +1078,13 @@
         <v>0.1931</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2151</v>
+        <v>0.131</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2207</v>
+        <v>0.1999</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0056</v>
+        <v>-0.0689</v>
       </c>
       <c r="V8" t="n">
         <v>-0.2856</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P. RODRIGUEZ FAJARDO</t>
+          <t>R. GONZALEZ GRANDE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.0922</v>
+        <v>-0.2208</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0207</v>
+        <v>-0.4975</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.1129</v>
+        <v>0.2767</v>
       </c>
       <c r="G9" t="n">
-        <v>1.6816</v>
+        <v>-0.06950000000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>-3.1517</v>
+        <v>-1.0416</v>
       </c>
       <c r="I9" t="n">
-        <v>4.8333</v>
+        <v>0.972</v>
       </c>
       <c r="J9" t="n">
-        <v>2.5585</v>
+        <v>0.8759</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.8408</v>
+        <v>0.0621</v>
       </c>
       <c r="L9" t="n">
-        <v>4.3993</v>
+        <v>0.8138</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.8769</v>
+        <v>-0.9454</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.3109</v>
+        <v>-1.1036</v>
       </c>
       <c r="O9" t="n">
-        <v>0.434</v>
+        <v>0.1582</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.5792</v>
+        <v>-1.5446</v>
       </c>
       <c r="Q9" t="n">
         <v>-1.9308</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3515</v>
+        <v>0.3862</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.0095</v>
+        <v>0.1656</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.607</v>
+        <v>-0.0139</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4025</v>
+        <v>0.1795</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.1851</v>
+        <v>1.2277</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.5712</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.1851</v>
+        <v>0.6565</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. DIAZ FELST</t>
+          <t>A. GOMEZ PEÑA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.3134</v>
+        <v>-0.5886</v>
       </c>
       <c r="E10" t="n">
-        <v>0.269</v>
+        <v>3.4541</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.5824</v>
+        <v>-4.0427</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.0512</v>
+        <v>-0.2121</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.8552999999999999</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.1959</v>
+        <v>0.4295</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.4853</v>
+        <v>3.1203</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0414</v>
+        <v>1.7729</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.5266999999999999</v>
+        <v>1.3474</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.5659</v>
+        <v>-3.3324</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.8967000000000001</v>
+        <v>-2.4145</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.6692</v>
+        <v>-0.9179</v>
       </c>
       <c r="P10" t="n">
-        <v>0.1931</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-0.9654</v>
       </c>
       <c r="R10" t="n">
-        <v>0.1931</v>
+        <v>0.9654</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2592</v>
+        <v>-0.0482</v>
       </c>
       <c r="T10" t="n">
-        <v>0.4688</v>
+        <v>-0.2141</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2096</v>
+        <v>0.1659</v>
       </c>
       <c r="V10" t="n">
-        <v>0.2856</v>
+        <v>-0.3282</v>
       </c>
       <c r="W10" t="n">
-        <v>0.2856</v>
+        <v>1.5133</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.8415</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. GOMEZ PEÑA</t>
+          <t>M. DIAZ FELST</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.4229</v>
+        <v>-1.6277</v>
       </c>
       <c r="E11" t="n">
-        <v>2.6198</v>
+        <v>-0.1447</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.0427</v>
+        <v>-1.4831</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.2121</v>
+        <v>-2.0512</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.6415999999999999</v>
+        <v>-0.8552999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>0.4295</v>
+        <v>-1.1959</v>
       </c>
       <c r="J11" t="n">
-        <v>3.1203</v>
+        <v>-0.4853</v>
       </c>
       <c r="K11" t="n">
-        <v>1.7729</v>
+        <v>0.0414</v>
       </c>
       <c r="L11" t="n">
-        <v>1.3474</v>
+        <v>-0.5266999999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>-3.3324</v>
+        <v>-1.5659</v>
       </c>
       <c r="N11" t="n">
-        <v>-2.4145</v>
+        <v>-0.8967000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.9179</v>
+        <v>-0.6692</v>
       </c>
       <c r="P11" t="n">
+        <v>0.1931</v>
+      </c>
+      <c r="Q11" t="n">
         <v>0</v>
       </c>
-      <c r="Q11" t="n">
-        <v>-0.9654</v>
-      </c>
       <c r="R11" t="n">
-        <v>0.9654</v>
+        <v>0.1931</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8826000000000001</v>
+        <v>-0.0552</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.0485</v>
+        <v>0.0551</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1659</v>
+        <v>-0.1102</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.3282</v>
+        <v>0.2856</v>
       </c>
       <c r="W11" t="n">
-        <v>1.5133</v>
+        <v>0.2856</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.8415</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.1064</v>
+        <v>-2.9753</v>
       </c>
       <c r="E12" t="n">
-        <v>0.5907</v>
+        <v>0.5977</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.6972</v>
+        <v>-3.573</v>
       </c>
       <c r="G12" t="n">
         <v>-0.8028999999999999</v>
@@ -1390,13 +1390,13 @@
         <v>0.1931</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3035</v>
+        <v>-0.1724</v>
       </c>
       <c r="T12" t="n">
-        <v>0.248</v>
+        <v>0.255</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5515</v>
+        <v>-0.4274</v>
       </c>
       <c r="V12" t="n">
         <v>-1.2277</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.1938</v>
+        <v>-4.2765</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.5451</v>
+        <v>-2.7519</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.6487</v>
+        <v>-1.5245</v>
       </c>
       <c r="G13" t="n">
         <v>-2.5522</v>
@@ -1468,13 +1468,13 @@
         <v>0.1931</v>
       </c>
       <c r="S13" t="n">
-        <v>0.3584</v>
+        <v>0.2758</v>
       </c>
       <c r="T13" t="n">
-        <v>0.3032</v>
+        <v>0.0964</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0552</v>
+        <v>0.1794</v>
       </c>
       <c r="V13" t="n">
         <v>-1.2277</v>
@@ -1501,16 +1501,16 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.499699999999999</v>
+        <v>4.051399999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>23.4519</v>
+        <v>24.0039</v>
       </c>
       <c r="F14" t="n">
         <v>-19.9524</v>
       </c>
       <c r="G14" t="n">
-        <v>4.3798</v>
+        <v>4.379800000000001</v>
       </c>
       <c r="H14" t="n">
         <v>-7.2399</v>
@@ -1546,16 +1546,16 @@
         <v>9.653999999999998</v>
       </c>
       <c r="S14" t="n">
-        <v>3.3098</v>
+        <v>3.8616</v>
       </c>
       <c r="T14" t="n">
-        <v>2.203199999999999</v>
+        <v>2.7551</v>
       </c>
       <c r="U14" t="n">
-        <v>1.1065</v>
+        <v>1.1064</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.3282000000000003</v>
+        <v>-0.3282000000000007</v>
       </c>
       <c r="W14" t="n">
         <v>8.9946</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>G. BERGERON</t>
+          <t>M. ROLDAN GAYOSO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.1366</v>
+        <v>5.2448</v>
       </c>
       <c r="E15" t="n">
-        <v>5.3352</v>
+        <v>6.9868</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.1987</v>
+        <v>-1.742</v>
       </c>
       <c r="G15" t="n">
-        <v>2.3357</v>
+        <v>1.0513</v>
       </c>
       <c r="H15" t="n">
-        <v>3.283</v>
+        <v>0.9789</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.9473</v>
+        <v>0.07240000000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>4.4958</v>
+        <v>3.7631</v>
       </c>
       <c r="K15" t="n">
-        <v>4.2493</v>
+        <v>2.0833</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2464</v>
+        <v>1.6798</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.1601</v>
+        <v>-2.7118</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.9664</v>
+        <v>-1.1044</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.1937</v>
+        <v>-1.6074</v>
       </c>
       <c r="P15" t="n">
-        <v>1.9308</v>
+        <v>0.1931</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.1931</v>
+        <v>-1.1585</v>
       </c>
       <c r="R15" t="n">
-        <v>2.1239</v>
+        <v>1.3515</v>
       </c>
       <c r="S15" t="n">
-        <v>1.4839</v>
+        <v>-0.2965</v>
       </c>
       <c r="T15" t="n">
-        <v>1.0752</v>
+        <v>-0.2004</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4088</v>
+        <v>-0.0961</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.6138</v>
+        <v>4.2969</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.0426</v>
+        <v>4.5825</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.5712</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. ROLDAN GAYOSO</t>
+          <t>G. BERGERON</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.8682</v>
+        <v>4.2388</v>
       </c>
       <c r="E16" t="n">
-        <v>6.8833</v>
+        <v>4.6113</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.0151</v>
+        <v>-0.3725</v>
       </c>
       <c r="G16" t="n">
-        <v>1.0513</v>
+        <v>2.3357</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9789</v>
+        <v>3.283</v>
       </c>
       <c r="I16" t="n">
-        <v>0.07240000000000001</v>
+        <v>-0.9473</v>
       </c>
       <c r="J16" t="n">
-        <v>3.7631</v>
+        <v>4.4958</v>
       </c>
       <c r="K16" t="n">
-        <v>2.0833</v>
+        <v>4.2493</v>
       </c>
       <c r="L16" t="n">
-        <v>1.6798</v>
+        <v>0.2464</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.7118</v>
+        <v>-2.1601</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.1044</v>
+        <v>-0.9664</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.6074</v>
+        <v>-1.1937</v>
       </c>
       <c r="P16" t="n">
-        <v>0.1931</v>
+        <v>1.9308</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1585</v>
+        <v>-0.1931</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3515</v>
+        <v>2.1239</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.673</v>
+        <v>0.5861</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3038</v>
+        <v>0.3512</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3692</v>
+        <v>0.2349</v>
       </c>
       <c r="V16" t="n">
-        <v>4.2969</v>
+        <v>-0.6138</v>
       </c>
       <c r="W16" t="n">
-        <v>4.5825</v>
+        <v>-0.0426</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2856</v>
+        <v>-0.5712</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. PIZARRO</t>
+          <t>J. MOLINA MELENDEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.3866</v>
+        <v>1.5599</v>
       </c>
       <c r="E17" t="n">
-        <v>3.2621</v>
+        <v>6.5825</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.8755</v>
+        <v>-5.0226</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.9731</v>
+        <v>1.9912</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.3107</v>
+        <v>1.7244</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.6624</v>
+        <v>0.2668</v>
       </c>
       <c r="J17" t="n">
-        <v>1.9519</v>
+        <v>6.6002</v>
       </c>
       <c r="K17" t="n">
-        <v>1.1381</v>
+        <v>3.6567</v>
       </c>
       <c r="L17" t="n">
-        <v>0.8138</v>
+        <v>2.9436</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.925</v>
+        <v>-4.609</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.4488</v>
+        <v>-1.9323</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.4763</v>
+        <v>-2.6767</v>
       </c>
       <c r="P17" t="n">
-        <v>1.1585</v>
+        <v>-0.3862</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-3.0892</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1585</v>
+        <v>2.7031</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3973</v>
+        <v>-0.9447</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0825</v>
+        <v>-0.2833</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4798</v>
+        <v>-0.6614</v>
       </c>
       <c r="V17" t="n">
-        <v>1.5985</v>
+        <v>0.8995</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2277</v>
+        <v>3.3548</v>
       </c>
       <c r="X17" t="n">
-        <v>0.3709</v>
+        <v>-2.4554</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. MOLINA MELENDEZ</t>
+          <t>M. PIZARRO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8441</v>
+        <v>1.4322</v>
       </c>
       <c r="E18" t="n">
-        <v>6.0654</v>
+        <v>3.1587</v>
       </c>
       <c r="F18" t="n">
-        <v>-5.2213</v>
+        <v>-1.7265</v>
       </c>
       <c r="G18" t="n">
-        <v>1.9912</v>
+        <v>-0.9731</v>
       </c>
       <c r="H18" t="n">
-        <v>1.7244</v>
+        <v>-0.3107</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2668</v>
+        <v>-0.6624</v>
       </c>
       <c r="J18" t="n">
-        <v>6.6002</v>
+        <v>1.9519</v>
       </c>
       <c r="K18" t="n">
-        <v>3.6567</v>
+        <v>1.1381</v>
       </c>
       <c r="L18" t="n">
-        <v>2.9436</v>
+        <v>0.8138</v>
       </c>
       <c r="M18" t="n">
-        <v>-4.609</v>
+        <v>-2.925</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.9323</v>
+        <v>-1.4488</v>
       </c>
       <c r="O18" t="n">
-        <v>-2.6767</v>
+        <v>-1.4763</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.3862</v>
+        <v>1.1585</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.0892</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.7031</v>
+        <v>1.1585</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.6604</v>
+        <v>-0.3517</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8004</v>
+        <v>-0.0209</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.86</v>
+        <v>-0.3308</v>
       </c>
       <c r="V18" t="n">
-        <v>0.8995</v>
+        <v>1.5985</v>
       </c>
       <c r="W18" t="n">
-        <v>3.3548</v>
+        <v>1.2277</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.4554</v>
+        <v>0.3709</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5211</v>
+        <v>0.8273</v>
       </c>
       <c r="E19" t="n">
-        <v>1.7646</v>
+        <v>1.9714</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.2434</v>
+        <v>-1.1441</v>
       </c>
       <c r="G19" t="n">
         <v>1.2192</v>
@@ -1936,13 +1936,13 @@
         <v>0.9654</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.0922</v>
+        <v>-0.7861</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.607</v>
+        <v>-0.4002</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4852</v>
+        <v>-0.3859</v>
       </c>
       <c r="V19" t="n">
         <v>-0.5712</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.4045</v>
+        <v>-2.8018</v>
       </c>
       <c r="E20" t="n">
         <v>-0.2662</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.1383</v>
+        <v>-2.5356</v>
       </c>
       <c r="G20" t="n">
         <v>-2.5138</v>
@@ -2014,13 +2014,13 @@
         <v>2.7031</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.09909999999999999</v>
+        <v>-0.4964</v>
       </c>
       <c r="T20" t="n">
         <v>-0.2213</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1222</v>
+        <v>-0.2751</v>
       </c>
       <c r="V20" t="n">
         <v>-0.3709</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-6.3652</v>
+        <v>-6.2329</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.1211</v>
+        <v>-1.9143</v>
       </c>
       <c r="F21" t="n">
-        <v>-4.2441</v>
+        <v>-4.3186</v>
       </c>
       <c r="G21" t="n">
         <v>-3.9846</v>
@@ -2092,13 +2092,13 @@
         <v>1.5446</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5737</v>
+        <v>-0.4414</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.359</v>
+        <v>-0.1521</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2147</v>
+        <v>-0.2892</v>
       </c>
       <c r="V21" t="n">
         <v>-1.2277</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-7.4866</v>
+        <v>-7.7679</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.9709</v>
+        <v>-1.1777</v>
       </c>
       <c r="F22" t="n">
-        <v>-6.5157</v>
+        <v>-6.5902</v>
       </c>
       <c r="G22" t="n">
         <v>-3.5057</v>
@@ -2170,13 +2170,13 @@
         <v>0.9654</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2978</v>
+        <v>-0.5790999999999999</v>
       </c>
       <c r="T22" t="n">
-        <v>0.0273</v>
+        <v>-0.1795</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3251</v>
+        <v>-0.3996</v>
       </c>
       <c r="V22" t="n">
         <v>-3.6831</v>
@@ -2203,10 +2203,10 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.499700000000001</v>
+        <v>-3.499600000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>19.9524</v>
+        <v>19.9525</v>
       </c>
       <c r="F23" t="n">
         <v>-23.4521</v>
@@ -2248,13 +2248,13 @@
         <v>13.5155</v>
       </c>
       <c r="S23" t="n">
-        <v>-3.309600000000001</v>
+        <v>-3.3098</v>
       </c>
       <c r="T23" t="n">
         <v>-1.1065</v>
       </c>
       <c r="U23" t="n">
-        <v>-2.203</v>
+        <v>-2.2032</v>
       </c>
       <c r="V23" t="n">
         <v>0.3282000000000007</v>
